--- a/frontend/public/templates/documents-import-template.xlsx
+++ b/frontend/public/templates/documents-import-template.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>建议填写：组内制度与通知、实验室安全、实验方法、项目与经费材料、论文写作与投稿、学位论文与参考资料、组会与学术交流、行政表格与模板。也可以填写分类 slug。</t>
+          <t>建议填写：组内制度与通知、实验室安全、实验方法、项目与经费材料、论文写作与投稿、其他参考资料、组会与学术交流、行政表格与模板。也可以填写分类 slug。</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>学位论文与参考资料</t>
+          <t>其他参考资料</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
